--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.9</v>
+        <v>21.46</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.46</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.2</v>
+        <v>21.51</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.51</v>
+        <v>20.03</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.87548905791384</v>
+        <v>32.08497705731303</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.39427639097158</v>
+        <v>34.74342305663691</v>
       </c>
     </row>
     <row r="9">
@@ -774,7 +774,7 @@
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>23.17542816591873</v>
+        <v>42.58701049427211</v>
       </c>
       <c r="F11" t="n">
-        <v>18.32529877992962</v>
+        <v>33.67444544559495</v>
       </c>
     </row>
     <row r="12">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>19.39427639097158</v>
+        <v>34.74342305663691</v>
       </c>
     </row>
     <row r="13">
@@ -1044,11 +1044,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.934387161004269</v>
+        <v>14.43450365361041</v>
       </c>
       <c r="C2" t="n">
-        <v>14.40493810945905</v>
+        <v>23.12950309594259</v>
       </c>
       <c r="D2" t="n">
-        <v>22.87548905791384</v>
+        <v>31.82450253827476</v>
       </c>
       <c r="E2" t="n">
-        <v>31.34604000636863</v>
+        <v>40.51950198060694</v>
       </c>
       <c r="F2" t="n">
-        <v>39.81659095482341</v>
+        <v>49.21450142293912</v>
       </c>
     </row>
     <row r="3">
@@ -1112,19 +1112,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.934387161004269</v>
+        <v>14.56474091312954</v>
       </c>
       <c r="C3" t="n">
-        <v>14.40493810945905</v>
+        <v>23.25974035546172</v>
       </c>
       <c r="D3" t="n">
-        <v>22.87548905791384</v>
+        <v>31.9547397977939</v>
       </c>
       <c r="E3" t="n">
-        <v>31.34604000636863</v>
+        <v>40.64973924012607</v>
       </c>
       <c r="F3" t="n">
-        <v>39.81659095482341</v>
+        <v>49.34473868245826</v>
       </c>
     </row>
     <row r="4">
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.934387161004269</v>
+        <v>14.69497817264868</v>
       </c>
       <c r="C4" t="n">
-        <v>14.40493810945905</v>
+        <v>23.38997761498085</v>
       </c>
       <c r="D4" t="n">
-        <v>22.87548905791384</v>
+        <v>32.08497705731303</v>
       </c>
       <c r="E4" t="n">
-        <v>31.34604000636863</v>
+        <v>40.7799764996452</v>
       </c>
       <c r="F4" t="n">
-        <v>39.81659095482341</v>
+        <v>49.47497594197739</v>
       </c>
     </row>
     <row r="5">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.934387161004269</v>
+        <v>14.82521543216781</v>
       </c>
       <c r="C5" t="n">
-        <v>14.40493810945905</v>
+        <v>23.52021487449998</v>
       </c>
       <c r="D5" t="n">
-        <v>22.87548905791384</v>
+        <v>32.21521431683216</v>
       </c>
       <c r="E5" t="n">
-        <v>31.34604000636863</v>
+        <v>40.91021375916434</v>
       </c>
       <c r="F5" t="n">
-        <v>39.81659095482341</v>
+        <v>49.60521320149651</v>
       </c>
     </row>
     <row r="6">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.934387161004269</v>
+        <v>14.95545269168694</v>
       </c>
       <c r="C6" t="n">
-        <v>14.40493810945905</v>
+        <v>23.65045213401911</v>
       </c>
       <c r="D6" t="n">
-        <v>22.87548905791384</v>
+        <v>32.34545157635129</v>
       </c>
       <c r="E6" t="n">
-        <v>31.34604000636863</v>
+        <v>41.04045101868346</v>
       </c>
       <c r="F6" t="n">
-        <v>39.81659095482341</v>
+        <v>49.73545046101565</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1228,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>29.67</v>
+        <v>32.85</v>
       </c>
     </row>
     <row r="3">
@@ -1236,7 +1236,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>30.94</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="4">
@@ -1244,7 +1244,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>31.36</v>
+        <v>33.04</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.03</v>
+        <v>20.71</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.71</v>
+        <v>20.87</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -12,7 +12,6 @@
     <sheet name="DivStrip" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Sensitivity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Payout" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Warnings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1250,35 +1249,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Data validation warnings</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>spot TCE VLCC: $388,300/day is 9.7x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.87</v>
+        <v>21.35</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.174610773689295e-24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.97215226305253e-29</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.35</v>
+        <v>21.68</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.68</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.6</v>
+        <v>22.49</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.49</v>
+        <v>22.31</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.31</v>
+        <v>22.38</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.38</v>
+        <v>22.685</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.685</v>
+        <v>22.19</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.19</v>
+        <v>22.46</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.46</v>
+        <v>23.35</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.35</v>
+        <v>22.39</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.39</v>
+        <v>22.37</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.08497705731303</v>
+        <v>29.96575112256588</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28.09730805832722</v>
+        <v>25.7017402916922</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>34.74342305663691</v>
+        <v>32.808425009815</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7737341072279861</v>
+        <v>0.7808162328292794</v>
       </c>
     </row>
     <row r="12">
@@ -611,7 +611,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5399.5</v>
+        <v>5363.475</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>585</v>
+        <v>649.09</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>546.352</v>
+        <v>268.901</v>
       </c>
     </row>
     <row r="5">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.852</v>
+        <v>-81.694</v>
       </c>
     </row>
     <row r="6">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-2602.942</v>
+        <v>-2930.832</v>
       </c>
     </row>
     <row r="7">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2251.5</v>
+        <v>-1697</v>
       </c>
     </row>
     <row r="9">
@@ -712,7 +712,7 @@
         <v/>
       </c>
       <c r="B10" t="n">
-        <v>1689.262</v>
+        <v>1571.94</v>
       </c>
     </row>
     <row r="11">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>60121845</v>
+        <v>61160839</v>
       </c>
     </row>
     <row r="12">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28.09730805832722</v>
+        <v>25.7017402916922</v>
       </c>
     </row>
     <row r="13">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28.09730805832722</v>
+        <v>25.7017402916922</v>
       </c>
     </row>
     <row r="14">
@@ -822,7 +822,7 @@
         <v>80557.14285714286</v>
       </c>
       <c r="D2" t="n">
-        <v>1.938242328557948</v>
+        <v>1.941997546011427</v>
       </c>
       <c r="E2" t="n">
         <v>0.15</v>
@@ -844,7 +844,7 @@
         <v>83557.14285714286</v>
       </c>
       <c r="D3" t="n">
-        <v>2.040569233196353</v>
+        <v>2.043732440459164</v>
       </c>
       <c r="E3" t="n">
         <v>0.15</v>
@@ -866,7 +866,7 @@
         <v>83057.14285714286</v>
       </c>
       <c r="D4" t="n">
-        <v>2.022640160161419</v>
+        <v>2.025821367493013</v>
       </c>
       <c r="E4" t="n">
         <v>0.15</v>
@@ -888,7 +888,7 @@
         <v>80357.14285714286</v>
       </c>
       <c r="D5" t="n">
-        <v>1.932120206058214</v>
+        <v>1.935979425494801</v>
       </c>
       <c r="E5" t="n">
         <v>0.15</v>
@@ -910,7 +910,7 @@
         <v>80757.14285714286</v>
       </c>
       <c r="D6" t="n">
-        <v>1.945676334450481</v>
+        <v>1.949448552365346</v>
       </c>
       <c r="E6" t="n">
         <v>0.15</v>
@@ -932,7 +932,7 @@
         <v>83557.14285714286</v>
       </c>
       <c r="D7" t="n">
-        <v>2.040569233196353</v>
+        <v>2.043732440459164</v>
       </c>
       <c r="E7" t="n">
         <v>0.15</v>
@@ -954,7 +954,7 @@
         <v>83057.14285714286</v>
       </c>
       <c r="D8" t="n">
-        <v>2.022640160161419</v>
+        <v>2.025821367493013</v>
       </c>
       <c r="E8" t="n">
         <v>0.15</v>
@@ -976,7 +976,7 @@
         <v>80557.14285714286</v>
       </c>
       <c r="D9" t="n">
-        <v>1.938242328557948</v>
+        <v>1.941997546011427</v>
       </c>
       <c r="E9" t="n">
         <v>0.15</v>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>42.58701049427211</v>
+        <v>40.13987941205319</v>
       </c>
       <c r="F11" t="n">
-        <v>33.67444544559495</v>
+        <v>31.73944739877304</v>
       </c>
     </row>
     <row r="12">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>34.74342305663691</v>
+        <v>32.808425009815</v>
       </c>
     </row>
     <row r="13">
@@ -1089,19 +1089,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14.43450365361041</v>
+        <v>12.53853207149281</v>
       </c>
       <c r="C2" t="n">
-        <v>23.12950309594259</v>
+        <v>21.12202638562886</v>
       </c>
       <c r="D2" t="n">
-        <v>31.82450253827476</v>
+        <v>29.70552069976489</v>
       </c>
       <c r="E2" t="n">
-        <v>40.51950198060694</v>
+        <v>38.28901501390094</v>
       </c>
       <c r="F2" t="n">
-        <v>49.21450142293912</v>
+        <v>46.87250932803698</v>
       </c>
     </row>
     <row r="3">
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14.56474091312954</v>
+        <v>12.66864728289331</v>
       </c>
       <c r="C3" t="n">
-        <v>23.25974035546172</v>
+        <v>21.25214159702935</v>
       </c>
       <c r="D3" t="n">
-        <v>31.9547397977939</v>
+        <v>29.83563591116539</v>
       </c>
       <c r="E3" t="n">
-        <v>40.64973924012607</v>
+        <v>38.41913022530143</v>
       </c>
       <c r="F3" t="n">
-        <v>49.34473868245826</v>
+        <v>47.00262453943747</v>
       </c>
     </row>
     <row r="4">
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.69497817264868</v>
+        <v>12.7987624942938</v>
       </c>
       <c r="C4" t="n">
-        <v>23.38997761498085</v>
+        <v>21.38225680842984</v>
       </c>
       <c r="D4" t="n">
-        <v>32.08497705731303</v>
+        <v>29.96575112256588</v>
       </c>
       <c r="E4" t="n">
-        <v>40.7799764996452</v>
+        <v>38.54924543670192</v>
       </c>
       <c r="F4" t="n">
-        <v>49.47497594197739</v>
+        <v>47.13273975083796</v>
       </c>
     </row>
     <row r="5">
@@ -1155,19 +1155,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.82521543216781</v>
+        <v>12.9288777056943</v>
       </c>
       <c r="C5" t="n">
-        <v>23.52021487449998</v>
+        <v>21.51237201983034</v>
       </c>
       <c r="D5" t="n">
-        <v>32.21521431683216</v>
+        <v>30.09586633396638</v>
       </c>
       <c r="E5" t="n">
-        <v>40.91021375916434</v>
+        <v>38.67936064810242</v>
       </c>
       <c r="F5" t="n">
-        <v>49.60521320149651</v>
+        <v>47.26285496223846</v>
       </c>
     </row>
     <row r="6">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.95545269168694</v>
+        <v>13.05899291709479</v>
       </c>
       <c r="C6" t="n">
-        <v>23.65045213401911</v>
+        <v>21.64248723123084</v>
       </c>
       <c r="D6" t="n">
-        <v>32.34545157635129</v>
+        <v>30.22598154536687</v>
       </c>
       <c r="E6" t="n">
-        <v>41.04045101868346</v>
+        <v>38.80947585950292</v>
       </c>
       <c r="F6" t="n">
-        <v>49.73545046101565</v>
+        <v>47.39297017363896</v>
       </c>
     </row>
   </sheetData>
@@ -1227,7 +1227,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>32.85</v>
+        <v>30.73</v>
       </c>
     </row>
     <row r="3">
@@ -1235,7 +1235,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>32.99</v>
+        <v>30.87</v>
       </c>
     </row>
     <row r="4">
@@ -1243,7 +1243,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>33.04</v>
+        <v>30.92</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.37</v>
+        <v>22.59</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.59</v>
+        <v>22.61</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.61</v>
+        <v>22.62</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/ccec_fv_report.xlsx
+++ b/outputs/ccec_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.62</v>
+        <v>22.72</v>
       </c>
     </row>
     <row r="5">
